--- a/Employee_Reports_wi52/Nino Vercide Arda Q0499.xlsx
+++ b/Employee_Reports_wi52/Nino Vercide Arda Q0499.xlsx
@@ -89,10 +89,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -578,362 +578,362 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>EXPIRING SOON</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>VNA Truck-K (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">LSME-QDF-M-001 </t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>08-Sep-2024</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>08-Sep-2026</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="H4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Stretch Wrapper (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-M-003</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>10-Aug-2026</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>09-Aug-2028</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>720</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="n">
+        <v>712</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Counter Balance Truck E-15 (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>LSME-QDF-M-005</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>10-Sep-2024</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>10-Sep-2026</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="H6" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Order Picker (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>LSME-QDF-M-006</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>04-Sep-2024</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>04-Sep-2026</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="H7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Bin Conveyor System (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-M-007</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>21-Jul-2025</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>21-Jul-2027</t>
         </is>
       </c>
-      <c r="H8" s="3" t="n">
-        <v>335</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
+        <v>327</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Pallet Conveyor System (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-M-008</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>16-Oct-2024</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>16-Oct-2026</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Pallet Stacker L-14 (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-M-010</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>11-Aug-2026</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>10-Aug-2028</t>
         </is>
       </c>
-      <c r="H10" s="3" t="n">
-        <v>721</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>713</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -970,166 +970,166 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>EXPIRING SOON</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Low Lift Truck T30 (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-M-015</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>21-Oct-2024</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>21-Oct-2026</t>
         </is>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Bizerba Weight (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>LSME-QDF-M-012</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>09-Sep-2024</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>09-Sep-2026</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="H13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>ASRS Stacker Crane (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-M-013</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>11-Aug-2026</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>10-Aug-2028</t>
         </is>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>721</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="H14" s="4" t="n">
+        <v>713</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1166,68 +1166,68 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>EXPIRING SOON</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Linde Software and ELOKON (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-M-009</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>14-Oct-2024</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>14-Oct-2026</t>
         </is>
       </c>
-      <c r="H16" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1264,865 +1264,865 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>VALID</t>
+          <t>EXPIRING SOON</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Stretch Wrapper Parameters (DFW Trainings)</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>QDFWH</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-M-004</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>10-Aug-2026</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>09-Aug-2028</t>
         </is>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>720</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
+      <c r="H18" s="4" t="n">
+        <v>712</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>22R1 Reefer Container (CBF Trainings)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>CBF&amp;AVI</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>LSME-CBF-02-004</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>28-Oct-2025</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>28-Oct-2027</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>434</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
+      <c r="H19" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Truck Dock 15FT (CBF Trainings)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>CBF&amp;AVI</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>LSME-CBF-02-002</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>27-Oct-2025</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>27-Oct-2027</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n">
-        <v>433</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="H20" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Powered Roller Deck- (CBF Trainings)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>CBF&amp;AVI</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">LSME-CBF-02-001 </t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>27-Oct-2025</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>27-Oct-2027</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n">
-        <v>433</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Tilting Deck2 (CBF Trainings)</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>CBF&amp;AVI</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>LSME-CBF-02-003</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>28-Oct-2025</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>28-Oct-2027</t>
         </is>
       </c>
-      <c r="H22" s="3" t="n">
-        <v>434</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
+      <c r="H22" s="4" t="n">
+        <v>426</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Castor Roller Deck  (CBF Trainings)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>CBF&amp;AVI</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>LSME-CBF-02-005</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>29-Oct-2025</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>29-Oct-2027</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>435</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="H23" s="4" t="n">
+        <v>427</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>WEIGHING SCALE (CBF Trainings)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>CBF&amp;AVI</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>LSME-CBF-02-006</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>29-Oct-2025</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>29-Oct-2027</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>435</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="n">
+        <v>427</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>AVI Equipment (CBF Trainings)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>CBF&amp;AVI</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>LSME-CBF-02-007</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>26-Oct-2025</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>26-Oct-2027</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
-        <v>432</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
+      <c r="H25" s="4" t="n">
+        <v>424</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Lodige LOTO Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>ELECTRICAL SAFETY</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>LSME-OHS-SOP-021</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>28-Jan-2026</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>28-Jan-2027</t>
         </is>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Endangered by Electricity A safety Training (SOPs)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>26-Sep-2025</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>26-Sep-2026</t>
         </is>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="H27" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Incident Escalation Process(LSME-IMS-SOP-021 ) (SOPs)</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-021</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>08-Apr-2026</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>08-Apr-2027</t>
         </is>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>231</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr"/>
+      <c r="H28" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-018</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>14-Apr-2026</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>14-Apr-2027</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
+      <c r="H29" s="4" t="n">
+        <v>229</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-022</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>11-Aug-2026</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>11-Aug-2027</t>
         </is>
       </c>
-      <c r="H30" s="3" t="n">
-        <v>356</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr"/>
+      <c r="H30" s="4" t="n">
+        <v>348</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Equipment Operation Procedure(QDF-SOP-003) (SOPs)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>DFWH</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-SOP-003</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>07-May-2027</t>
         </is>
       </c>
-      <c r="H31" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="H31" s="4" t="n">
+        <v>252</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Matar LOTO Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>MATAR</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>FM-DE-24-SOP-SA-013</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>04-Dec-2025</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>04-Dec-2026</t>
         </is>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
+      <c r="H32" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>VNA Truck Emergency Lowering Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>DFWH</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>LSME-QDF-SOP-008</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>12-Aug-2026</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>12-Aug-2027</t>
         </is>
       </c>
-      <c r="H33" s="3" t="n">
-        <v>357</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
+      <c r="H33" s="4" t="n">
+        <v>349</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>10-Jul-2025</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>10-Jul-2027</t>
         </is>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>324</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
+      <c r="H34" s="4" t="n">
+        <v>316</v>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>BCP for QDF-ASRS And MHE Due To Equipment failure (Other Trainings)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>12-Aug-2026</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>11-Aug-2028</t>
         </is>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>722</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="n">
+        <v>714</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2191,66 +2191,66 @@
       <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Reach Truck R16</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>28-Oct-2024</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>83.12%</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Approved Score. date is valid</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n"/>
+      <c r="G3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Vna Truck-K</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>21-Oct-2024</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>perfect score</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Congratulations on achieving a perfect score!!!! date is valid</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -2315,66 +2315,66 @@
       <c r="G6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Bin Conveyor System</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>31-Jul-2025</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>80.00%</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Approved Score. date is valid</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n"/>
+      <c r="G7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Pallet Conveyor System</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>11-Nov-2024</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>88.46%</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Approved Score. date is valid</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -2408,21 +2408,21 @@
       <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>TOTAL AVERAGE</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>79.58%</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="n"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
